--- a/output/pdf_financials_xlsx/QQQ.xlsx
+++ b/output/pdf_financials_xlsx/QQQ.xlsx
@@ -612,10 +612,10 @@
         <v>0</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>0.000212</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>1.4e-05</v>
       </c>
     </row>
     <row r="13">
@@ -864,10 +864,10 @@
         <v>-0.210154</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-0.556683</v>
+        <v>-0.556895</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-2.049548</v>
+        <v>-2.049562</v>
       </c>
     </row>
     <row r="28">
@@ -896,10 +896,10 @@
         <v>-0.210154</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-0.556683</v>
+        <v>-0.556895</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-2.049548</v>
+        <v>-2.049562</v>
       </c>
     </row>
     <row r="30">
@@ -976,13 +976,13 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.06432499999999999</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.178901</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.243393</v>
       </c>
     </row>
     <row r="35">
@@ -1008,13 +1008,13 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.06432499999999999</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.178901</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.243393</v>
       </c>
     </row>
     <row r="37">
@@ -1200,13 +1200,13 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.09699199999999999</v>
+        <v>0.032667</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.270492</v>
+        <v>0.09159100000000001</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.419836</v>
+        <v>0.176443</v>
       </c>
     </row>
     <row r="49">
@@ -2685,7 +2685,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" s="5" t="n">
@@ -5112,7 +5112,7 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">

--- a/output/pdf_financials_xlsx/QQQ.xlsx
+++ b/output/pdf_financials_xlsx/QQQ.xlsx
@@ -1510,13 +1510,13 @@
         </is>
       </c>
       <c r="B67" s="3" t="n">
-        <v>0</v>
+        <v>0.023</v>
       </c>
       <c r="C67" s="3" t="n">
-        <v>0</v>
+        <v>0.03</v>
       </c>
       <c r="D67" s="3" t="n">
-        <v>0</v>
+        <v>0.0204</v>
       </c>
     </row>
     <row r="68">
@@ -2051,13 +2051,13 @@
         </is>
       </c>
       <c r="B101" s="3" t="n">
-        <v>0</v>
+        <v>-0.007667</v>
       </c>
       <c r="C101" s="3" t="n">
-        <v>0</v>
+        <v>-0.016236</v>
       </c>
       <c r="D101" s="3" t="n">
-        <v>0</v>
+        <v>0.007532</v>
       </c>
     </row>
     <row r="102">
@@ -2131,13 +2131,13 @@
         </is>
       </c>
       <c r="B106" s="3" t="n">
-        <v>0.034798</v>
+        <v>0.027131</v>
       </c>
       <c r="C106" s="3" t="n">
-        <v>0.017944</v>
+        <v>0.001708</v>
       </c>
       <c r="D106" s="3" t="n">
-        <v>-0.15472</v>
+        <v>-0.147188</v>
       </c>
     </row>
     <row r="107">
@@ -3276,7 +3276,11 @@
           <t>GST recoverable</t>
         </is>
       </c>
-      <c r="D21" t="inlineStr"/>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>ChangeInReceivables</t>
+        </is>
+      </c>
       <c r="E21" s="5" t="n">
         <v>-0.007667</v>
       </c>
@@ -4380,7 +4384,11 @@
           <t>Deferred income tax recovery</t>
         </is>
       </c>
-      <c r="D57" t="inlineStr"/>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E57" s="5" t="n">
         <v>-0.016958</v>
       </c>
